--- a/src/Data/LoginexcelData.xlsx
+++ b/src/Data/LoginexcelData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CHINMAY\Dipti_PW_Framework\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CHINMAY\Dipti_PW_Framework\src\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_F25DC773A252ABDACC1048F0F91978945ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F38FDFA5-AE5E-4096-B9E2-FF4915D7AC5F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41937F9A-B54D-4A33-8939-E7C1DD4F2D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,13 +42,13 @@
     <t>wrong123</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>pw123</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
+    <t>xxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  xxx</t>
   </si>
 </sst>
 </file>
@@ -398,10 +398,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
